--- a/lessons.xlsx
+++ b/lessons.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F145D43-5E26-4BF2-BD93-6F3A7FF6C8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{851F2735-0EFF-48BE-8326-0ECD7233E03D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,6 @@
     <sheet name="Lists" sheetId="3" state="hidden" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -101,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="163">
   <si>
     <t>Категорија</t>
   </si>
@@ -554,13 +553,49 @@
   </si>
   <si>
     <t>Осна симетрија и транслација - вежби</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbxC1SFz5L4gA7uNJ1fUf_4uoQax8B8U4sIAYGkzhHQLH8Xs9htYpOPCFJyXNNiAxZ6WFA/exec</t>
+  </si>
+  <si>
+    <t>Ротација</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbwWuzL2se0T0mLBDvDIgdLRVj4VE3pglcE-WtJjJXiknqhXY6Qm9HRMBmBGIxDVmf2jow/exec</t>
+  </si>
+  <si>
+    <t>Решава проблеми со маса, должина и зафатнина</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbzhquDDP01uVDobJFUVsBTw79132DDxnH21C_sXmCxLZYuI3zCK8r7iDFnzaUvIO9SP/exec</t>
+  </si>
+  <si>
+    <t>Примена на Питагорова теорема</t>
+  </si>
+  <si>
+    <t>Споредување цени дадени во различни валути</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbwm1HrLVb56EXheipy9go4kYrPgHu4cmqg1ocgHqKaM0OfZQfsXj-cWl6DOdDsGJvPEgw/exec</t>
+  </si>
+  <si>
+    <t>Поим за релација</t>
+  </si>
+  <si>
+    <t>https://ik-cod.github.io/Matematika/data/8</t>
+  </si>
+  <si>
+    <t>Операции со множества</t>
+  </si>
+  <si>
+    <t>https://ik-cod.github.io/Matematika/data/7</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -605,6 +640,14 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -685,10 +728,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -724,8 +768,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
@@ -750,12 +798,13 @@
   <autoFilter ref="A1:E736" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Геометрија"/>
+        <filter val="Броеви"/>
       </filters>
     </filterColumn>
     <filterColumn colId="1">
       <filters>
         <filter val="7"/>
+        <filter val="8"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1067,7 +1116,7 @@
     <col min="5" max="5" width="88" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1686,7 +1735,7 @@
       </c>
       <c r="E41" s="11"/>
     </row>
-    <row r="42" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>5</v>
       </c>
@@ -1697,11 +1746,13 @@
         <v>1</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="E42" s="11"/>
-    </row>
-    <row r="43" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>5</v>
       </c>
@@ -1716,7 +1767,7 @@
       </c>
       <c r="E43" s="11"/>
     </row>
-    <row r="44" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>5</v>
       </c>
@@ -1731,7 +1782,7 @@
       </c>
       <c r="E44" s="11"/>
     </row>
-    <row r="45" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>5</v>
       </c>
@@ -1746,7 +1797,7 @@
       </c>
       <c r="E45" s="11"/>
     </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>5</v>
       </c>
@@ -1759,7 +1810,7 @@
       <c r="D46" s="5"/>
       <c r="E46" s="11"/>
     </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>5</v>
       </c>
@@ -1772,7 +1823,7 @@
       <c r="D47" s="5"/>
       <c r="E47" s="11"/>
     </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>5</v>
       </c>
@@ -1785,7 +1836,7 @@
       <c r="D48" s="5"/>
       <c r="E48" s="11"/>
     </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>5</v>
       </c>
@@ -1798,7 +1849,7 @@
       <c r="D49" s="5"/>
       <c r="E49" s="11"/>
     </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>5</v>
       </c>
@@ -1811,7 +1862,7 @@
       <c r="D50" s="5"/>
       <c r="E50" s="11"/>
     </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>5</v>
       </c>
@@ -1824,7 +1875,7 @@
       <c r="D51" s="5"/>
       <c r="E51" s="11"/>
     </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>5</v>
       </c>
@@ -1837,7 +1888,7 @@
       <c r="D52" s="5"/>
       <c r="E52" s="11"/>
     </row>
-    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>5</v>
       </c>
@@ -1850,7 +1901,7 @@
       <c r="D53" s="5"/>
       <c r="E53" s="11"/>
     </row>
-    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>5</v>
       </c>
@@ -1863,7 +1914,7 @@
       <c r="D54" s="5"/>
       <c r="E54" s="11"/>
     </row>
-    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>5</v>
       </c>
@@ -1876,7 +1927,7 @@
       <c r="D55" s="5"/>
       <c r="E55" s="11"/>
     </row>
-    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>5</v>
       </c>
@@ -1889,7 +1940,7 @@
       <c r="D56" s="5"/>
       <c r="E56" s="11"/>
     </row>
-    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>5</v>
       </c>
@@ -1902,7 +1953,7 @@
       <c r="D57" s="5"/>
       <c r="E57" s="11"/>
     </row>
-    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>5</v>
       </c>
@@ -1915,7 +1966,7 @@
       <c r="D58" s="5"/>
       <c r="E58" s="11"/>
     </row>
-    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>5</v>
       </c>
@@ -1928,7 +1979,7 @@
       <c r="D59" s="5"/>
       <c r="E59" s="11"/>
     </row>
-    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>5</v>
       </c>
@@ -1941,7 +1992,7 @@
       <c r="D60" s="5"/>
       <c r="E60" s="11"/>
     </row>
-    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>5</v>
       </c>
@@ -1954,7 +2005,7 @@
       <c r="D61" s="5"/>
       <c r="E61" s="11"/>
     </row>
-    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>5</v>
       </c>
@@ -1967,7 +2018,7 @@
       <c r="D62" s="5"/>
       <c r="E62" s="11"/>
     </row>
-    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>5</v>
       </c>
@@ -1980,7 +2031,7 @@
       <c r="D63" s="5"/>
       <c r="E63" s="11"/>
     </row>
-    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>5</v>
       </c>
@@ -1993,7 +2044,7 @@
       <c r="D64" s="5"/>
       <c r="E64" s="11"/>
     </row>
-    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>5</v>
       </c>
@@ -2006,7 +2057,7 @@
       <c r="D65" s="5"/>
       <c r="E65" s="11"/>
     </row>
-    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>5</v>
       </c>
@@ -2019,7 +2070,7 @@
       <c r="D66" s="5"/>
       <c r="E66" s="11"/>
     </row>
-    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>5</v>
       </c>
@@ -2032,7 +2083,7 @@
       <c r="D67" s="5"/>
       <c r="E67" s="11"/>
     </row>
-    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>5</v>
       </c>
@@ -2045,7 +2096,7 @@
       <c r="D68" s="5"/>
       <c r="E68" s="11"/>
     </row>
-    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>5</v>
       </c>
@@ -2058,7 +2109,7 @@
       <c r="D69" s="5"/>
       <c r="E69" s="11"/>
     </row>
-    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>5</v>
       </c>
@@ -2071,7 +2122,7 @@
       <c r="D70" s="5"/>
       <c r="E70" s="11"/>
     </row>
-    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>5</v>
       </c>
@@ -2084,7 +2135,7 @@
       <c r="D71" s="5"/>
       <c r="E71" s="11"/>
     </row>
-    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>5</v>
       </c>
@@ -2097,7 +2148,7 @@
       <c r="D72" s="5"/>
       <c r="E72" s="11"/>
     </row>
-    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>5</v>
       </c>
@@ -2110,7 +2161,7 @@
       <c r="D73" s="5"/>
       <c r="E73" s="11"/>
     </row>
-    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>5</v>
       </c>
@@ -2123,7 +2174,7 @@
       <c r="D74" s="5"/>
       <c r="E74" s="11"/>
     </row>
-    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>5</v>
       </c>
@@ -2136,7 +2187,7 @@
       <c r="D75" s="5"/>
       <c r="E75" s="11"/>
     </row>
-    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>5</v>
       </c>
@@ -2149,7 +2200,7 @@
       <c r="D76" s="5"/>
       <c r="E76" s="11"/>
     </row>
-    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>5</v>
       </c>
@@ -2162,7 +2213,7 @@
       <c r="D77" s="5"/>
       <c r="E77" s="11"/>
     </row>
-    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>5</v>
       </c>
@@ -2175,7 +2226,7 @@
       <c r="D78" s="5"/>
       <c r="E78" s="11"/>
     </row>
-    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>5</v>
       </c>
@@ -2188,7 +2239,7 @@
       <c r="D79" s="5"/>
       <c r="E79" s="11"/>
     </row>
-    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>5</v>
       </c>
@@ -2201,7 +2252,7 @@
       <c r="D80" s="5"/>
       <c r="E80" s="11"/>
     </row>
-    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>5</v>
       </c>
@@ -2214,7 +2265,7 @@
       <c r="D81" s="5"/>
       <c r="E81" s="11"/>
     </row>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>5</v>
       </c>
@@ -2224,10 +2275,14 @@
       <c r="C82" s="4">
         <v>1</v>
       </c>
-      <c r="D82" s="5"/>
-      <c r="E82" s="11"/>
-    </row>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D82" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E82" s="13" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>5</v>
       </c>
@@ -2240,7 +2295,7 @@
       <c r="D83" s="5"/>
       <c r="E83" s="11"/>
     </row>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>5</v>
       </c>
@@ -2253,7 +2308,7 @@
       <c r="D84" s="5"/>
       <c r="E84" s="11"/>
     </row>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>5</v>
       </c>
@@ -2266,7 +2321,7 @@
       <c r="D85" s="5"/>
       <c r="E85" s="11"/>
     </row>
-    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>5</v>
       </c>
@@ -2279,7 +2334,7 @@
       <c r="D86" s="5"/>
       <c r="E86" s="11"/>
     </row>
-    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>5</v>
       </c>
@@ -2292,7 +2347,7 @@
       <c r="D87" s="5"/>
       <c r="E87" s="11"/>
     </row>
-    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>5</v>
       </c>
@@ -2305,7 +2360,7 @@
       <c r="D88" s="5"/>
       <c r="E88" s="11"/>
     </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>5</v>
       </c>
@@ -2318,7 +2373,7 @@
       <c r="D89" s="5"/>
       <c r="E89" s="11"/>
     </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>5</v>
       </c>
@@ -2331,7 +2386,7 @@
       <c r="D90" s="5"/>
       <c r="E90" s="11"/>
     </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>5</v>
       </c>
@@ -2344,7 +2399,7 @@
       <c r="D91" s="5"/>
       <c r="E91" s="11"/>
     </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>5</v>
       </c>
@@ -2357,7 +2412,7 @@
       <c r="D92" s="5"/>
       <c r="E92" s="11"/>
     </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>5</v>
       </c>
@@ -2370,7 +2425,7 @@
       <c r="D93" s="5"/>
       <c r="E93" s="11"/>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>5</v>
       </c>
@@ -2383,7 +2438,7 @@
       <c r="D94" s="5"/>
       <c r="E94" s="11"/>
     </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>5</v>
       </c>
@@ -2396,7 +2451,7 @@
       <c r="D95" s="5"/>
       <c r="E95" s="11"/>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>5</v>
       </c>
@@ -2409,7 +2464,7 @@
       <c r="D96" s="5"/>
       <c r="E96" s="11"/>
     </row>
-    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>5</v>
       </c>
@@ -2422,7 +2477,7 @@
       <c r="D97" s="5"/>
       <c r="E97" s="11"/>
     </row>
-    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>5</v>
       </c>
@@ -2435,7 +2490,7 @@
       <c r="D98" s="5"/>
       <c r="E98" s="11"/>
     </row>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>5</v>
       </c>
@@ -2448,7 +2503,7 @@
       <c r="D99" s="5"/>
       <c r="E99" s="11"/>
     </row>
-    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>5</v>
       </c>
@@ -2461,7 +2516,7 @@
       <c r="D100" s="5"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>5</v>
       </c>
@@ -2474,7 +2529,7 @@
       <c r="D101" s="5"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>5</v>
       </c>
@@ -2487,7 +2542,7 @@
       <c r="D102" s="5"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>5</v>
       </c>
@@ -2500,7 +2555,7 @@
       <c r="D103" s="5"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>5</v>
       </c>
@@ -2513,7 +2568,7 @@
       <c r="D104" s="5"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>5</v>
       </c>
@@ -2526,7 +2581,7 @@
       <c r="D105" s="5"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>5</v>
       </c>
@@ -2539,7 +2594,7 @@
       <c r="D106" s="5"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>5</v>
       </c>
@@ -2552,7 +2607,7 @@
       <c r="D107" s="5"/>
       <c r="E107" s="11"/>
     </row>
-    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>5</v>
       </c>
@@ -2565,7 +2620,7 @@
       <c r="D108" s="5"/>
       <c r="E108" s="11"/>
     </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>5</v>
       </c>
@@ -2578,7 +2633,7 @@
       <c r="D109" s="5"/>
       <c r="E109" s="11"/>
     </row>
-    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
         <v>5</v>
       </c>
@@ -2591,7 +2646,7 @@
       <c r="D110" s="5"/>
       <c r="E110" s="11"/>
     </row>
-    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
         <v>5</v>
       </c>
@@ -2604,7 +2659,7 @@
       <c r="D111" s="5"/>
       <c r="E111" s="11"/>
     </row>
-    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
         <v>5</v>
       </c>
@@ -2617,7 +2672,7 @@
       <c r="D112" s="5"/>
       <c r="E112" s="11"/>
     </row>
-    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>5</v>
       </c>
@@ -2630,7 +2685,7 @@
       <c r="D113" s="5"/>
       <c r="E113" s="11"/>
     </row>
-    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
         <v>5</v>
       </c>
@@ -2643,7 +2698,7 @@
       <c r="D114" s="5"/>
       <c r="E114" s="11"/>
     </row>
-    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
         <v>5</v>
       </c>
@@ -2656,7 +2711,7 @@
       <c r="D115" s="5"/>
       <c r="E115" s="11"/>
     </row>
-    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
         <v>5</v>
       </c>
@@ -2669,7 +2724,7 @@
       <c r="D116" s="5"/>
       <c r="E116" s="11"/>
     </row>
-    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>5</v>
       </c>
@@ -2682,7 +2737,7 @@
       <c r="D117" s="5"/>
       <c r="E117" s="11"/>
     </row>
-    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>5</v>
       </c>
@@ -2695,7 +2750,7 @@
       <c r="D118" s="5"/>
       <c r="E118" s="11"/>
     </row>
-    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>5</v>
       </c>
@@ -2708,7 +2763,7 @@
       <c r="D119" s="5"/>
       <c r="E119" s="11"/>
     </row>
-    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>5</v>
       </c>
@@ -2721,7 +2776,7 @@
       <c r="D120" s="5"/>
       <c r="E120" s="11"/>
     </row>
-    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>5</v>
       </c>
@@ -6159,7 +6214,7 @@
       <c r="D376" s="5"/>
       <c r="E376" s="11"/>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="4" t="s">
         <v>44</v>
       </c>
@@ -6176,7 +6231,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" s="4" t="s">
         <v>44</v>
       </c>
@@ -6189,7 +6244,7 @@
       <c r="D378" s="5"/>
       <c r="E378" s="11"/>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="4" t="s">
         <v>44</v>
       </c>
@@ -6202,7 +6257,7 @@
       <c r="D379" s="5"/>
       <c r="E379" s="11"/>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="4" t="s">
         <v>44</v>
       </c>
@@ -6215,7 +6270,7 @@
       <c r="D380" s="5"/>
       <c r="E380" s="11"/>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="4" t="s">
         <v>44</v>
       </c>
@@ -6228,7 +6283,7 @@
       <c r="D381" s="5"/>
       <c r="E381" s="11"/>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" s="4" t="s">
         <v>44</v>
       </c>
@@ -6241,7 +6296,7 @@
       <c r="D382" s="5"/>
       <c r="E382" s="11"/>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" s="4" t="s">
         <v>44</v>
       </c>
@@ -6254,7 +6309,7 @@
       <c r="D383" s="5"/>
       <c r="E383" s="11"/>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" s="4" t="s">
         <v>44</v>
       </c>
@@ -6267,7 +6322,7 @@
       <c r="D384" s="5"/>
       <c r="E384" s="11"/>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" s="4" t="s">
         <v>44</v>
       </c>
@@ -6280,7 +6335,7 @@
       <c r="D385" s="5"/>
       <c r="E385" s="11"/>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" s="4" t="s">
         <v>44</v>
       </c>
@@ -6297,7 +6352,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" s="4" t="s">
         <v>44</v>
       </c>
@@ -6307,10 +6362,14 @@
       <c r="C387" s="4">
         <v>11</v>
       </c>
-      <c r="D387" s="5"/>
-      <c r="E387" s="11"/>
-    </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D387" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E387" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" s="4" t="s">
         <v>44</v>
       </c>
@@ -6323,7 +6382,7 @@
       <c r="D388" s="5"/>
       <c r="E388" s="11"/>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" s="4" t="s">
         <v>44</v>
       </c>
@@ -6336,7 +6395,7 @@
       <c r="D389" s="5"/>
       <c r="E389" s="11"/>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" s="4" t="s">
         <v>44</v>
       </c>
@@ -6349,7 +6408,7 @@
       <c r="D390" s="5"/>
       <c r="E390" s="11"/>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" s="4" t="s">
         <v>44</v>
       </c>
@@ -6362,7 +6421,7 @@
       <c r="D391" s="5"/>
       <c r="E391" s="11"/>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" s="4" t="s">
         <v>44</v>
       </c>
@@ -6375,7 +6434,7 @@
       <c r="D392" s="5"/>
       <c r="E392" s="11"/>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" s="4" t="s">
         <v>44</v>
       </c>
@@ -6388,7 +6447,7 @@
       <c r="D393" s="5"/>
       <c r="E393" s="11"/>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" s="4" t="s">
         <v>44</v>
       </c>
@@ -6401,7 +6460,7 @@
       <c r="D394" s="5"/>
       <c r="E394" s="11"/>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" s="4" t="s">
         <v>44</v>
       </c>
@@ -6414,7 +6473,7 @@
       <c r="D395" s="5"/>
       <c r="E395" s="11"/>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" s="4" t="s">
         <v>44</v>
       </c>
@@ -6427,7 +6486,7 @@
       <c r="D396" s="5"/>
       <c r="E396" s="11"/>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" s="4" t="s">
         <v>44</v>
       </c>
@@ -6440,7 +6499,7 @@
       <c r="D397" s="5"/>
       <c r="E397" s="11"/>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" s="4" t="s">
         <v>44</v>
       </c>
@@ -6453,7 +6512,7 @@
       <c r="D398" s="5"/>
       <c r="E398" s="11"/>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" s="4" t="s">
         <v>44</v>
       </c>
@@ -6466,7 +6525,7 @@
       <c r="D399" s="5"/>
       <c r="E399" s="11"/>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" s="4" t="s">
         <v>44</v>
       </c>
@@ -6479,7 +6538,7 @@
       <c r="D400" s="5"/>
       <c r="E400" s="11"/>
     </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" s="4" t="s">
         <v>44</v>
       </c>
@@ -6492,7 +6551,7 @@
       <c r="D401" s="5"/>
       <c r="E401" s="11"/>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" s="4" t="s">
         <v>44</v>
       </c>
@@ -6505,7 +6564,7 @@
       <c r="D402" s="5"/>
       <c r="E402" s="11"/>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" s="4" t="s">
         <v>44</v>
       </c>
@@ -6518,7 +6577,7 @@
       <c r="D403" s="5"/>
       <c r="E403" s="11"/>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" s="4" t="s">
         <v>44</v>
       </c>
@@ -6531,7 +6590,7 @@
       <c r="D404" s="5"/>
       <c r="E404" s="11"/>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" s="4" t="s">
         <v>44</v>
       </c>
@@ -6544,7 +6603,7 @@
       <c r="D405" s="5"/>
       <c r="E405" s="11"/>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" s="4" t="s">
         <v>44</v>
       </c>
@@ -6557,7 +6616,7 @@
       <c r="D406" s="5"/>
       <c r="E406" s="11"/>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" s="4" t="s">
         <v>44</v>
       </c>
@@ -6570,7 +6629,7 @@
       <c r="D407" s="5"/>
       <c r="E407" s="11"/>
     </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" s="4" t="s">
         <v>44</v>
       </c>
@@ -6583,7 +6642,7 @@
       <c r="D408" s="5"/>
       <c r="E408" s="11"/>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" s="4" t="s">
         <v>44</v>
       </c>
@@ -6596,7 +6655,7 @@
       <c r="D409" s="5"/>
       <c r="E409" s="11"/>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" s="4" t="s">
         <v>44</v>
       </c>
@@ -6609,7 +6668,7 @@
       <c r="D410" s="5"/>
       <c r="E410" s="11"/>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" s="4" t="s">
         <v>44</v>
       </c>
@@ -6622,7 +6681,7 @@
       <c r="D411" s="5"/>
       <c r="E411" s="11"/>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" s="4" t="s">
         <v>44</v>
       </c>
@@ -6635,7 +6694,7 @@
       <c r="D412" s="5"/>
       <c r="E412" s="11"/>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" s="4" t="s">
         <v>44</v>
       </c>
@@ -6648,7 +6707,7 @@
       <c r="D413" s="5"/>
       <c r="E413" s="11"/>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" s="4" t="s">
         <v>44</v>
       </c>
@@ -6661,7 +6720,7 @@
       <c r="D414" s="5"/>
       <c r="E414" s="11"/>
     </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" s="4" t="s">
         <v>44</v>
       </c>
@@ -6674,7 +6733,7 @@
       <c r="D415" s="5"/>
       <c r="E415" s="11"/>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" s="4" t="s">
         <v>44</v>
       </c>
@@ -6687,7 +6746,7 @@
       <c r="D416" s="5"/>
       <c r="E416" s="11"/>
     </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" s="4" t="s">
         <v>44</v>
       </c>
@@ -6700,7 +6759,7 @@
       <c r="D417" s="5"/>
       <c r="E417" s="11"/>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" s="4" t="s">
         <v>44</v>
       </c>
@@ -6713,7 +6772,7 @@
       <c r="D418" s="5"/>
       <c r="E418" s="11"/>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" s="4" t="s">
         <v>44</v>
       </c>
@@ -6726,7 +6785,7 @@
       <c r="D419" s="5"/>
       <c r="E419" s="11"/>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" s="4" t="s">
         <v>44</v>
       </c>
@@ -6739,7 +6798,7 @@
       <c r="D420" s="5"/>
       <c r="E420" s="11"/>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" s="4" t="s">
         <v>44</v>
       </c>
@@ -6752,7 +6811,7 @@
       <c r="D421" s="5"/>
       <c r="E421" s="11"/>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" s="4" t="s">
         <v>44</v>
       </c>
@@ -6765,7 +6824,7 @@
       <c r="D422" s="5"/>
       <c r="E422" s="11"/>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" s="4" t="s">
         <v>44</v>
       </c>
@@ -6778,7 +6837,7 @@
       <c r="D423" s="5"/>
       <c r="E423" s="11"/>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" s="4" t="s">
         <v>44</v>
       </c>
@@ -6791,7 +6850,7 @@
       <c r="D424" s="5"/>
       <c r="E424" s="11"/>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" s="4" t="s">
         <v>44</v>
       </c>
@@ -6804,7 +6863,7 @@
       <c r="D425" s="5"/>
       <c r="E425" s="11"/>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" s="4" t="s">
         <v>44</v>
       </c>
@@ -6817,7 +6876,7 @@
       <c r="D426" s="5"/>
       <c r="E426" s="11"/>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" s="4" t="s">
         <v>44</v>
       </c>
@@ -6830,7 +6889,7 @@
       <c r="D427" s="5"/>
       <c r="E427" s="11"/>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" s="4" t="s">
         <v>44</v>
       </c>
@@ -6843,7 +6902,7 @@
       <c r="D428" s="5"/>
       <c r="E428" s="11"/>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" s="4" t="s">
         <v>44</v>
       </c>
@@ -6856,7 +6915,7 @@
       <c r="D429" s="5"/>
       <c r="E429" s="11"/>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" s="4" t="s">
         <v>44</v>
       </c>
@@ -6869,7 +6928,7 @@
       <c r="D430" s="5"/>
       <c r="E430" s="11"/>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" s="4" t="s">
         <v>44</v>
       </c>
@@ -8455,8 +8514,12 @@
       <c r="C551" s="4">
         <v>6</v>
       </c>
-      <c r="D551" s="5"/>
-      <c r="E551" s="11"/>
+      <c r="D551" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="E551" s="11" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="552" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552" s="4" t="s">
@@ -8533,8 +8596,12 @@
       <c r="C557" s="4">
         <v>12</v>
       </c>
-      <c r="D557" s="5"/>
-      <c r="E557" s="11"/>
+      <c r="D557" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="E557" s="11" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="558" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558" s="4" t="s">
@@ -9140,7 +9207,7 @@
       <c r="D603" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="E603" s="11" t="s">
+      <c r="E603" s="13" t="s">
         <v>147</v>
       </c>
     </row>
@@ -9658,8 +9725,12 @@
       <c r="C642" s="4">
         <v>11</v>
       </c>
-      <c r="D642" s="5"/>
-      <c r="E642" s="11"/>
+      <c r="D642" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E642" s="11" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="643" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A643" s="4" t="s">
@@ -10904,10 +10975,14 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E603" r:id="rId1" xr:uid="{C4BB2320-73F4-4247-B6EF-4A48501D6F90}"/>
+    <hyperlink ref="E82" r:id="rId2" xr:uid="{822F4467-6A29-45B0-81B1-6A7C3274ED07}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
